--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,25 +141,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>GEN</t>
-  </si>
-  <si>
     <t>Genomic</t>
   </si>
   <si>
-    <t>TSC</t>
+    <t>Transcriptomic-Single-Cell</t>
   </si>
   <si>
     <t>Transcriptomic Single Cell</t>
   </si>
   <si>
-    <t>TS</t>
-  </si>
-  <si>
     <t>Transcriptomic</t>
   </si>
   <si>
-    <t>GSC</t>
+    <t>Genomic-Single-Cell</t>
   </si>
   <si>
     <t>Genomic Single Cell</t>
@@ -497,7 +491,7 @@
         <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -506,10 +500,10 @@
         <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>45</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -518,10 +512,10 @@
         <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -530,10 +524,10 @@
         <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2"/>
     </row>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,19 +141,25 @@
     <t>1</t>
   </si>
   <si>
+    <t>GEN</t>
+  </si>
+  <si>
     <t>Genomic</t>
   </si>
   <si>
-    <t>Transcriptomic-Single-Cell</t>
+    <t>TSC</t>
   </si>
   <si>
     <t>Transcriptomic Single Cell</t>
   </si>
   <si>
+    <t>TS</t>
+  </si>
+  <si>
     <t>Transcriptomic</t>
   </si>
   <si>
-    <t>Genomic-Single-Cell</t>
+    <t>GSC</t>
   </si>
   <si>
     <t>Genomic Single Cell</t>
@@ -491,7 +497,7 @@
         <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -500,10 +506,10 @@
         <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -512,10 +518,10 @@
         <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -524,10 +530,10 @@
         <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2"/>
     </row>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-sequencing-experiment-source.xlsx
+++ b/docs/CodeSystem-sequencing-experiment-source.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Concepts" r:id="rId4" sheetId="2"/>
+    <sheet name="Properties" r:id="rId4" sheetId="2"/>
+    <sheet name="Concepts" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Sequencing experimental source</t>
+    <t>Experimental category of the experiment (Genomics, Transcriptomics, Epigenomics, Proteomics, Multi-omic, Clinical).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -123,15 +124,33 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>deprecated</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecated</t>
+  </si>
+  <si>
+    <t>The date at which a concept was deprecated. Concepts that are deprecated but not inactive can still be used, but their use is discouraged.</t>
+  </si>
+  <si>
+    <t>dateTime</t>
   </si>
   <si>
     <t>Level</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
     <t>Display</t>
   </si>
   <si>
@@ -144,19 +163,43 @@
     <t>GEN</t>
   </si>
   <si>
-    <t>Genomic</t>
+    <t>Genomics</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>Transcriptomics</t>
+  </si>
+  <si>
+    <t>EPI</t>
+  </si>
+  <si>
+    <t>Epigenomics</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>Proteomics</t>
+  </si>
+  <si>
+    <t>MUL</t>
+  </si>
+  <si>
+    <t>Multi-omic</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>Clinical</t>
   </si>
   <si>
     <t>TSC</t>
   </si>
   <si>
     <t>Transcriptomic Single Cell</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>Transcriptomic</t>
   </si>
   <si>
     <t>GSC</t>
@@ -472,7 +515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -483,59 +526,145 @@
         <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>39</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>41</v>
       </c>
+      <c r="C2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
